--- a/artfynd/A 18326-2024 artfynd.xlsx
+++ b/artfynd/A 18326-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118093598</v>
+        <v>118093349</v>
       </c>
       <c r="B2" t="n">
-        <v>57304</v>
+        <v>94612</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gårdsmad (Gårdsmad), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315894</v>
+        <v>315879</v>
       </c>
       <c r="R2" t="n">
-        <v>6547526</v>
+        <v>6547496</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118093349</v>
+        <v>118093598</v>
       </c>
       <c r="B3" t="n">
-        <v>94612</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gårdsmad (Gårdsmad), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315879</v>
+        <v>315894</v>
       </c>
       <c r="R3" t="n">
-        <v>6547496</v>
+        <v>6547526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18326-2024 artfynd.xlsx
+++ b/artfynd/A 18326-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>118093349</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdsmad (Gårdsmad), Dls</t>
+          <t>Gårdsmad, Gårdsmad, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -790,12 +785,7 @@
         <v>118093833</v>
       </c>
       <c r="B3" t="n">
-        <v>94620</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsmad (Gårdsmad), Dls</t>
+          <t>Gårdsmad, Gårdsmad, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -899,58 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118093598</v>
+        <v>118210657</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsmad (Gårdsmad), Dls</t>
+          <t>Skog öster om Stora Tresticklan, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>315894</v>
+        <v>315872</v>
       </c>
       <c r="R4" t="n">
-        <v>6547526</v>
+        <v>6547627</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,67 +974,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anton Larsson, Stefan Husar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118210659</v>
+        <v>118210655</v>
       </c>
       <c r="B5" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog öster om Stora Tresticklan, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>315988</v>
+        <v>315811</v>
       </c>
       <c r="R5" t="n">
-        <v>6547675</v>
+        <v>6547581</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,21 +1067,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118210654</v>
+        <v>118210656</v>
       </c>
       <c r="B6" t="n">
-        <v>90488</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>315787</v>
+        <v>315822</v>
       </c>
       <c r="R6" t="n">
-        <v>6547559</v>
+        <v>6547585</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,21 +1164,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118210656</v>
+        <v>118210654</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>315822</v>
+        <v>315787</v>
       </c>
       <c r="R7" t="n">
-        <v>6547585</v>
+        <v>6547559</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,6 +1261,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118210655</v>
+        <v>118210658</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>315811</v>
+        <v>315894</v>
       </c>
       <c r="R8" t="n">
-        <v>6547581</v>
+        <v>6547630</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,8 +1371,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1459,15 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118210658</v>
+        <v>118093598</v>
       </c>
       <c r="B9" t="n">
-        <v>90913</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1416,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog öster om Stora Tresticklan, Dls</t>
+          <t>Gårdsmad, Gårdsmad, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>315894</v>
       </c>
       <c r="R9" t="n">
-        <v>6547630</v>
+        <v>6547526</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,12 +1475,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,49 +1499,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson, Stefan Husar</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118210657</v>
+        <v>118210659</v>
       </c>
       <c r="B10" t="n">
-        <v>95433</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,34 +1528,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog öster om Stora Tresticklan, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>315872</v>
+        <v>315988</v>
       </c>
       <c r="R10" t="n">
-        <v>6547627</v>
+        <v>6547675</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1663,6 +1603,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 18326-2024 artfynd.xlsx
+++ b/artfynd/A 18326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118093349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118093833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210656</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210654</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118093598</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,8 +1676,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118210659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>